--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130339893</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130339883</v>
       </c>
       <c r="B3" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130339910</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -675,39 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130339893</v>
+        <v>130339883</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>106016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -785,35 +781,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130339883</v>
+        <v>130339893</v>
       </c>
       <c r="B3" t="n">
-        <v>105990</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -894,7 +894,7 @@
         <v>130339910</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130339883</v>
       </c>
       <c r="B2" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130339893</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130339910</v>
       </c>
       <c r="B4" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130339883</v>
       </c>
       <c r="B2" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130339893</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130339910</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130339883</v>
       </c>
       <c r="B2" t="n">
-        <v>106018</v>
+        <v>106020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130339893</v>
       </c>
       <c r="B3" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130339910</v>
       </c>
       <c r="B4" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130339883</v>
       </c>
       <c r="B2" t="n">
-        <v>106020</v>
+        <v>106024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130339893</v>
       </c>
       <c r="B3" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130339910</v>
       </c>
       <c r="B4" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130339883</v>
       </c>
       <c r="B2" t="n">
-        <v>106024</v>
+        <v>106037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130339893</v>
       </c>
       <c r="B3" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130339910</v>
       </c>
       <c r="B4" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -675,35 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130339883</v>
+        <v>130339893</v>
       </c>
       <c r="B2" t="n">
-        <v>106037</v>
+        <v>98971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -781,39 +785,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130339893</v>
+        <v>130339883</v>
       </c>
       <c r="B3" t="n">
-        <v>98970</v>
+        <v>106038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -894,7 +894,7 @@
         <v>130339910</v>
       </c>
       <c r="B4" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -675,39 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130339893</v>
+        <v>130339883</v>
       </c>
       <c r="B2" t="n">
-        <v>98971</v>
+        <v>106041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -785,35 +781,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130339883</v>
+        <v>130339893</v>
       </c>
       <c r="B3" t="n">
-        <v>106038</v>
+        <v>98974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -894,7 +894,7 @@
         <v>130339910</v>
       </c>
       <c r="B4" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -675,35 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130339883</v>
+        <v>130339893</v>
       </c>
       <c r="B2" t="n">
-        <v>106041</v>
+        <v>98974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -781,39 +785,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130339893</v>
+        <v>130339883</v>
       </c>
       <c r="B3" t="n">
-        <v>98974</v>
+        <v>106041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>

--- a/artfynd/A 62889-2025 artfynd.xlsx
+++ b/artfynd/A 62889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130339893</v>
       </c>
       <c r="B2" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130339883</v>
+        <v>130339910</v>
       </c>
       <c r="B3" t="n">
-        <v>106041</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593889</v>
+        <v>593881</v>
       </c>
       <c r="R3" t="n">
-        <v>6427722</v>
+        <v>6427533</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,32 +891,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130339910</v>
+        <v>130339883</v>
       </c>
       <c r="B4" t="n">
-        <v>98974</v>
+        <v>106243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593881</v>
+        <v>593889</v>
       </c>
       <c r="R4" t="n">
-        <v>6427533</v>
+        <v>6427722</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
